--- a/data/trans_orig/P6603-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P6603-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>279435</t>
+          <t>278134</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>308138</t>
+          <t>308236</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>184597</t>
+          <t>185007</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>202592</t>
+          <t>202813</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>470103</t>
+          <t>470362</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>503774</t>
+          <t>504700</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>88,04%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29474</t>
+          <t>29377</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53716</t>
+          <t>54241</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8097</t>
+          <t>8335</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22674</t>
+          <t>23096</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42400</t>
+          <t>42959</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>72382</t>
+          <t>71822</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,53%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9200</t>
+          <t>8929</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23853</t>
+          <t>24111</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12852</t>
+          <t>12595</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13479</t>
+          <t>13654</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30946</t>
+          <t>31388</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14429</t>
+          <t>14846</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6472</t>
+          <t>7243</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>3894</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15673</t>
+          <t>15828</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>216794</t>
+          <t>217161</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>241997</t>
+          <t>242515</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>215356</t>
+          <t>215366</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>227880</t>
+          <t>227837</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>438078</t>
+          <t>438261</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>466897</t>
+          <t>466807</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,85%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13984</t>
+          <t>14428</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32877</t>
+          <t>33961</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1686</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10422</t>
+          <t>10707</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17931</t>
+          <t>17667</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39748</t>
+          <t>39861</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4288</t>
+          <t>4545</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19302</t>
+          <t>19468</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11006</t>
+          <t>11708</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8202</t>
+          <t>8118</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>25386</t>
+          <t>25224</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2650</t>
+          <t>1877</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14070</t>
+          <t>13249</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2263</t>
+          <t>2675</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13546</t>
+          <t>14121</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>206015</t>
+          <t>205017</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>244789</t>
+          <t>242679</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>30182</t>
+          <t>29411</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>44260</t>
+          <t>44290</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>50,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>241700</t>
+          <t>241698</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>281638</t>
+          <t>282748</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,33%</t>
+          <t>64,59%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>66210</t>
+          <t>67263</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>98953</t>
+          <t>99830</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4805</t>
+          <t>4177</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15523</t>
+          <t>15517</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>75578</t>
+          <t>75293</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>109470</t>
+          <t>110010</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,13%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36881</t>
+          <t>35653</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>63221</t>
+          <t>62427</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5509</t>
+          <t>5754</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16526</t>
+          <t>17706</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>46676</t>
+          <t>46513</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>73743</t>
+          <t>74720</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,07%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15851</t>
+          <t>15823</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35172</t>
+          <t>35720</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>5013</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16375</t>
+          <t>16283</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>37889</t>
+          <t>36041</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>423909</t>
+          <t>421250</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>476721</t>
+          <t>472582</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>254946</t>
+          <t>255472</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>278858</t>
+          <t>278563</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>684914</t>
+          <t>683474</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>744920</t>
+          <t>743842</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>73,39%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>115141</t>
+          <t>116864</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>158552</t>
+          <t>161499</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>18898</t>
+          <t>19155</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>38169</t>
+          <t>38973</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>143712</t>
+          <t>140527</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>190002</t>
+          <t>189103</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,66%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>76441</t>
+          <t>75243</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>113087</t>
+          <t>112494</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3738</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15713</t>
+          <t>16864</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>84023</t>
+          <t>85279</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>122106</t>
+          <t>123954</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,23%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19596</t>
+          <t>20122</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>43034</t>
+          <t>41128</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8189</t>
+          <t>7478</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>22141</t>
+          <t>21543</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>44619</t>
+          <t>45428</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>85468</t>
+          <t>85362</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>113276</t>
+          <t>113489</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>130478</t>
+          <t>129322</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>158291</t>
+          <t>157797</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>223322</t>
+          <t>223342</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>262623</t>
+          <t>262768</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>66,29%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25095</t>
+          <t>26693</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>48363</t>
+          <t>48679</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>31412</t>
+          <t>30740</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>55936</t>
+          <t>56206</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>62264</t>
+          <t>64487</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>95276</t>
+          <t>96611</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,37%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>28434</t>
+          <t>28736</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>51437</t>
+          <t>52206</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8409</t>
+          <t>8466</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23802</t>
+          <t>23639</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>41131</t>
+          <t>41589</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>69575</t>
+          <t>69573</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5408</t>
+          <t>5463</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>18823</t>
+          <t>18898</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4488</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>17028</t>
+          <t>17459</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>12350</t>
+          <t>12287</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>30946</t>
+          <t>30611</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -3578,12 +3578,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1253208</t>
+          <t>1251520</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1337096</t>
+          <t>1336136</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>845076</t>
+          <t>842658</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>890475</t>
+          <t>889304</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3628,12 +3628,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2116222</t>
+          <t>2117139</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2212781</t>
+          <t>2212330</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3663,12 +3663,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>75,67%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>284495</t>
+          <t>286617</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>352672</t>
+          <t>354269</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>80696</t>
+          <t>81518</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>118340</t>
+          <t>119157</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>377904</t>
+          <t>380610</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>457834</t>
+          <t>457620</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,65%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>180537</t>
+          <t>180629</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>236448</t>
+          <t>237614</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>32025</t>
+          <t>32456</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>59508</t>
+          <t>59005</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>221812</t>
+          <t>221459</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>284459</t>
+          <t>281404</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>60564</t>
+          <t>61106</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>96903</t>
+          <t>98598</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>7515</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>23039</t>
+          <t>22916</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>73948</t>
+          <t>74009</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>111932</t>
+          <t>111954</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4380,12 +4380,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>198151</t>
+          <t>196405</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>232611</t>
+          <t>231299</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>152634</t>
+          <t>152802</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>173668</t>
+          <t>173760</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>79,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>358526</t>
+          <t>359616</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>398859</t>
+          <t>401430</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,9%</t>
         </is>
       </c>
     </row>
@@ -4493,12 +4493,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46376</t>
+          <t>47157</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>76408</t>
+          <t>78202</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4528,12 +4528,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11774</t>
+          <t>12314</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30473</t>
+          <t>30068</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>62687</t>
+          <t>62280</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>97534</t>
+          <t>96329</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,41%</t>
         </is>
       </c>
     </row>
@@ -4606,12 +4606,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11168</t>
+          <t>11135</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30272</t>
+          <t>32759</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4786</t>
+          <t>4652</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17627</t>
+          <t>17604</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4656,12 +4656,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18927</t>
+          <t>19490</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>43975</t>
+          <t>44129</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,89%</t>
         </is>
       </c>
     </row>
@@ -4719,12 +4719,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3801</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17109</t>
+          <t>17288</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4734,12 +4734,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5239</t>
+          <t>4716</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4185</t>
+          <t>4028</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19631</t>
+          <t>17546</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4804,12 +4804,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -4949,12 +4949,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>174928</t>
+          <t>174872</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>205101</t>
+          <t>206251</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>139194</t>
+          <t>139055</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>156167</t>
+          <t>155996</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4999,12 +4999,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>321504</t>
+          <t>322272</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>356378</t>
+          <t>357250</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,57%</t>
         </is>
       </c>
     </row>
@@ -5062,12 +5062,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34721</t>
+          <t>34059</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60555</t>
+          <t>60707</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5077,12 +5077,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6063</t>
+          <t>6066</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20275</t>
+          <t>19714</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5112,12 +5112,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43975</t>
+          <t>43956</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>75819</t>
+          <t>72680</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,2%</t>
         </is>
       </c>
     </row>
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4573</t>
+          <t>4795</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18874</t>
+          <t>19410</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6728</t>
+          <t>6342</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6149</t>
+          <t>6123</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>21800</t>
+          <t>22582</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5260,12 +5260,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -5288,12 +5288,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3849</t>
+          <t>3761</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19486</t>
+          <t>17674</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5303,12 +5303,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11444</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5779</t>
+          <t>4886</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>23104</t>
+          <t>21208</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -5518,12 +5518,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>111505</t>
+          <t>112082</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>144114</t>
+          <t>143531</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5533,12 +5533,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>67534</t>
+          <t>67655</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>86587</t>
+          <t>86345</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5568,12 +5568,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>184866</t>
+          <t>185068</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>225512</t>
+          <t>227026</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5603,12 +5603,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>58,13%</t>
         </is>
       </c>
     </row>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>51840</t>
+          <t>51738</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>80015</t>
+          <t>79882</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5646,12 +5646,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5666,12 +5666,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10020</t>
+          <t>9943</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23756</t>
+          <t>23901</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5681,12 +5681,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5701,12 +5701,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>64964</t>
+          <t>67619</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>98005</t>
+          <t>97521</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>24,97%</t>
         </is>
       </c>
     </row>
@@ -5744,12 +5744,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43053</t>
+          <t>42567</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>70345</t>
+          <t>70608</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5759,12 +5759,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5779,12 +5779,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6168</t>
+          <t>6020</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19748</t>
+          <t>18982</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5794,12 +5794,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5814,12 +5814,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52638</t>
+          <t>53387</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>85274</t>
+          <t>84898</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5829,12 +5829,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,74%</t>
         </is>
       </c>
     </row>
@@ -5857,12 +5857,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20741</t>
+          <t>19995</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43896</t>
+          <t>41390</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5872,12 +5872,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2908</t>
+          <t>2872</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12995</t>
+          <t>13756</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5927,12 +5927,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25913</t>
+          <t>25131</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>49924</t>
+          <t>49939</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5942,12 +5942,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,79%</t>
         </is>
       </c>
     </row>
@@ -6087,12 +6087,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>203601</t>
+          <t>202929</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>244982</t>
+          <t>245149</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6102,12 +6102,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6122,12 +6122,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>217478</t>
+          <t>218409</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>248883</t>
+          <t>247814</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6137,12 +6137,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6157,12 +6157,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>432127</t>
+          <t>431216</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>485116</t>
+          <t>486682</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6172,12 +6172,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>67,25%</t>
         </is>
       </c>
     </row>
@@ -6200,12 +6200,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>99824</t>
+          <t>100159</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>138805</t>
+          <t>140886</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6215,12 +6215,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6235,12 +6235,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>27148</t>
+          <t>27204</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>50745</t>
+          <t>51413</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6250,12 +6250,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6270,12 +6270,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>134253</t>
+          <t>134045</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>180234</t>
+          <t>177782</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6285,12 +6285,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,56%</t>
         </is>
       </c>
     </row>
@@ -6313,12 +6313,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>38880</t>
+          <t>39269</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>64605</t>
+          <t>66378</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6328,12 +6328,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6348,12 +6348,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7126</t>
+          <t>7289</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>22592</t>
+          <t>24025</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6363,12 +6363,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6383,12 +6383,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>50059</t>
+          <t>48942</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>80436</t>
+          <t>80896</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6398,12 +6398,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,18%</t>
         </is>
       </c>
     </row>
@@ -6426,12 +6426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20200</t>
+          <t>21430</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>43010</t>
+          <t>43006</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -6461,12 +6461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7101</t>
+          <t>7062</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22363</t>
+          <t>22325</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6496,12 +6496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>33266</t>
+          <t>31753</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>59105</t>
+          <t>58357</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -6656,12 +6656,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>46074</t>
+          <t>45552</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>71194</t>
+          <t>69567</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6671,12 +6671,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>97920</t>
+          <t>98188</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>124485</t>
+          <t>123956</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>150677</t>
+          <t>151607</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>190225</t>
+          <t>188590</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>57,41%</t>
         </is>
       </c>
     </row>
@@ -6769,12 +6769,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>30427</t>
+          <t>29769</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>52235</t>
+          <t>53065</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6784,12 +6784,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6804,12 +6804,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>34045</t>
+          <t>33566</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>58789</t>
+          <t>56904</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>69452</t>
+          <t>70024</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>103265</t>
+          <t>102142</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,09%</t>
         </is>
       </c>
     </row>
@@ -6882,12 +6882,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>21908</t>
+          <t>21345</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>42887</t>
+          <t>41965</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6897,12 +6897,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6659</t>
+          <t>6502</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>20884</t>
+          <t>20299</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>31893</t>
+          <t>32234</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>57010</t>
+          <t>57655</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,55%</t>
         </is>
       </c>
     </row>
@@ -6995,12 +6995,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>14910</t>
+          <t>13952</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>33424</t>
+          <t>33877</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7010,12 +7010,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>12869</t>
+          <t>12440</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>18763</t>
+          <t>19183</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>40441</t>
+          <t>39557</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,04%</t>
         </is>
       </c>
     </row>
@@ -7225,12 +7225,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>779188</t>
+          <t>776032</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>857095</t>
+          <t>860781</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7240,12 +7240,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7260,12 +7260,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>708492</t>
+          <t>709345</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>761548</t>
+          <t>763073</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1507061</t>
+          <t>1506696</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1601993</t>
+          <t>1603607</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>67,91%</t>
         </is>
       </c>
     </row>
@@ -7338,12 +7338,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>297431</t>
+          <t>293191</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>367284</t>
+          <t>362185</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7353,12 +7353,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7373,12 +7373,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>108099</t>
+          <t>107677</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>152475</t>
+          <t>153214</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>415562</t>
+          <t>421771</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>498463</t>
+          <t>503318</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,31%</t>
         </is>
       </c>
     </row>
@@ -7451,12 +7451,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>145710</t>
+          <t>143759</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>194236</t>
+          <t>193783</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7466,12 +7466,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7486,12 +7486,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>37785</t>
+          <t>36128</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>66421</t>
+          <t>64986</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7521,12 +7521,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>187486</t>
+          <t>188918</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>247504</t>
+          <t>247523</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7536,7 +7536,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -7564,12 +7564,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>78666</t>
+          <t>81369</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>120281</t>
+          <t>123239</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7579,12 +7579,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7599,12 +7599,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>20666</t>
+          <t>20489</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>43780</t>
+          <t>42117</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>104160</t>
+          <t>107322</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>152538</t>
+          <t>152730</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -8027,12 +8027,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>191441</t>
+          <t>192528</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>222625</t>
+          <t>221400</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8042,12 +8042,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>165300</t>
+          <t>164631</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>187399</t>
+          <t>186561</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>366292</t>
+          <t>364989</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>403767</t>
+          <t>403112</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8112,12 +8112,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,2%</t>
         </is>
       </c>
     </row>
@@ -8140,12 +8140,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32347</t>
+          <t>33613</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59170</t>
+          <t>59225</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8155,12 +8155,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15893</t>
+          <t>16124</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34416</t>
+          <t>34687</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>54318</t>
+          <t>54101</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>86260</t>
+          <t>86223</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8225,12 +8225,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,58%</t>
         </is>
       </c>
     </row>
@@ -8253,12 +8253,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14250</t>
+          <t>13777</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32025</t>
+          <t>31833</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8268,12 +8268,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2830</t>
+          <t>2864</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12547</t>
+          <t>13334</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8303,12 +8303,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18350</t>
+          <t>20284</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>39585</t>
+          <t>41159</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8338,12 +8338,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -8371,7 +8371,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9009</t>
+          <t>9117</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8386,7 +8386,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8401,12 +8401,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>1877</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11483</t>
+          <t>10862</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8416,12 +8416,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3004</t>
+          <t>3072</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15224</t>
+          <t>15604</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8451,12 +8451,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -8596,12 +8596,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>171147</t>
+          <t>170355</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>197288</t>
+          <t>197562</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8611,12 +8611,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>145520</t>
+          <t>147027</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>165887</t>
+          <t>166653</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8646,12 +8646,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>321988</t>
+          <t>322160</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>357340</t>
+          <t>358327</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8681,12 +8681,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,89%</t>
         </is>
       </c>
     </row>
@@ -8709,12 +8709,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28687</t>
+          <t>29361</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52720</t>
+          <t>54321</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8724,12 +8724,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12302</t>
+          <t>12616</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27814</t>
+          <t>28811</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46823</t>
+          <t>46469</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>75619</t>
+          <t>75568</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8794,12 +8794,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,48%</t>
         </is>
       </c>
     </row>
@@ -8822,12 +8822,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10070</t>
+          <t>9965</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25369</t>
+          <t>25649</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8837,12 +8837,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4490</t>
+          <t>4987</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17518</t>
+          <t>17981</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8872,12 +8872,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17271</t>
+          <t>17369</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>39896</t>
+          <t>37329</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8907,12 +8907,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -8940,7 +8940,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7316</t>
+          <t>5792</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>933</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>8268</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8990,7 +8990,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>1871</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10790</t>
+          <t>11095</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9025,7 +9025,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -9165,12 +9165,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>74598</t>
+          <t>76072</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>104747</t>
+          <t>106870</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9180,12 +9180,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>41871</t>
+          <t>41567</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>56685</t>
+          <t>55919</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9215,12 +9215,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>122323</t>
+          <t>120746</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>155972</t>
+          <t>156211</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9250,12 +9250,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>55,42%</t>
         </is>
       </c>
     </row>
@@ -9278,12 +9278,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>57615</t>
+          <t>57603</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>84659</t>
+          <t>85420</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9298,7 +9298,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3713</t>
+          <t>3740</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15023</t>
+          <t>15340</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9328,12 +9328,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>64646</t>
+          <t>64710</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>95036</t>
+          <t>94515</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9363,12 +9363,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,53%</t>
         </is>
       </c>
     </row>
@@ -9391,12 +9391,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25203</t>
+          <t>26353</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47306</t>
+          <t>49721</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9406,12 +9406,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3860</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14850</t>
+          <t>15137</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9441,12 +9441,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33155</t>
+          <t>33110</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>58308</t>
+          <t>57275</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9476,12 +9476,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,32%</t>
         </is>
       </c>
     </row>
@@ -9504,12 +9504,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9802</t>
+          <t>10586</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27175</t>
+          <t>28270</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9519,12 +9519,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6468</t>
+          <t>5599</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9559,7 +9559,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10855</t>
+          <t>11175</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>29884</t>
+          <t>28770</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9589,12 +9589,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -9734,12 +9734,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>230692</t>
+          <t>231455</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>274682</t>
+          <t>275643</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9749,12 +9749,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>263627</t>
+          <t>264365</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>297799</t>
+          <t>296290</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9784,12 +9784,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>503109</t>
+          <t>506656</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>557664</t>
+          <t>562865</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9819,12 +9819,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>66,1%</t>
         </is>
       </c>
     </row>
@@ -9847,12 +9847,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>106661</t>
+          <t>110363</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>147472</t>
+          <t>147992</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9862,12 +9862,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40804</t>
+          <t>43143</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>70844</t>
+          <t>71636</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9897,12 +9897,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>162727</t>
+          <t>160318</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>209135</t>
+          <t>209466</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9932,12 +9932,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,6%</t>
         </is>
       </c>
     </row>
@@ -9960,12 +9960,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>67267</t>
+          <t>66233</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>101006</t>
+          <t>100306</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9975,12 +9975,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13614</t>
+          <t>13599</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>31610</t>
+          <t>31284</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10010,12 +10010,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>86326</t>
+          <t>85789</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>124561</t>
+          <t>126437</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,85%</t>
         </is>
       </c>
     </row>
@@ -10073,12 +10073,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11642</t>
+          <t>12832</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29003</t>
+          <t>30095</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10088,12 +10088,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5108</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20446</t>
+          <t>20643</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20767</t>
+          <t>20245</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>42574</t>
+          <t>43112</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -10303,12 +10303,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>52726</t>
+          <t>52658</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>79965</t>
+          <t>79821</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>106433</t>
+          <t>106267</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>134660</t>
+          <t>133554</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10353,12 +10353,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>166328</t>
+          <t>166406</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>205272</t>
+          <t>205534</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,62%</t>
         </is>
       </c>
     </row>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>64992</t>
+          <t>65248</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>95519</t>
+          <t>93001</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10431,12 +10431,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>43138</t>
+          <t>42654</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>67644</t>
+          <t>67545</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10466,12 +10466,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>118103</t>
+          <t>115670</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>154922</t>
+          <t>152935</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,15%</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>42512</t>
+          <t>43022</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10549,7 +10549,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10364</t>
+          <t>10021</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>26070</t>
+          <t>27094</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10579,12 +10579,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>35848</t>
+          <t>35302</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>62367</t>
+          <t>62175</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10614,12 +10614,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,92%</t>
         </is>
       </c>
     </row>
@@ -10642,12 +10642,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>10645</t>
+          <t>10380</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>27693</t>
+          <t>28324</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10657,12 +10657,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -10677,12 +10677,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>9701</t>
+          <t>10431</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10692,12 +10692,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -10712,12 +10712,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>13746</t>
+          <t>13813</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>32377</t>
+          <t>32347</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10727,12 +10727,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,28%</t>
         </is>
       </c>
     </row>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>759418</t>
+          <t>764014</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>840885</t>
+          <t>839588</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>759312</t>
+          <t>756692</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>812368</t>
+          <t>810475</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10922,12 +10922,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>78,37%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1537325</t>
+          <t>1534198</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1632813</t>
+          <t>1633631</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10957,12 +10957,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>62,71%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>66,77%</t>
         </is>
       </c>
     </row>
@@ -10985,12 +10985,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>329480</t>
+          <t>331582</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>400574</t>
+          <t>403969</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11000,12 +11000,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>140545</t>
+          <t>140099</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>186334</t>
+          <t>185420</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>486218</t>
+          <t>480698</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>568330</t>
+          <t>565830</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11070,12 +11070,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,13%</t>
         </is>
       </c>
     </row>
@@ -11098,12 +11098,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>163514</t>
+          <t>163881</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>215436</t>
+          <t>215051</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11113,12 +11113,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>48265</t>
+          <t>49139</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>79265</t>
+          <t>80246</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11148,12 +11148,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>223107</t>
+          <t>222274</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>281949</t>
+          <t>283069</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11183,12 +11183,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -11211,12 +11211,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>44078</t>
+          <t>45218</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>75377</t>
+          <t>75769</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11226,12 +11226,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>15784</t>
+          <t>15178</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>36717</t>
+          <t>35024</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11261,12 +11261,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>66486</t>
+          <t>64774</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>101504</t>
+          <t>100648</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11296,12 +11296,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -11669,32 +11669,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>150764</t>
+          <t>166211</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>140228</t>
+          <t>151568</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>159523</t>
+          <t>176459</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11704,32 +11704,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>129467</t>
+          <t>138343</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>121565</t>
+          <t>129388</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>135876</t>
+          <t>145070</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11739,32 +11739,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>280230</t>
+          <t>304556</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>266897</t>
+          <t>287911</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>292236</t>
+          <t>316534</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>79,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>87,69%</t>
         </is>
       </c>
     </row>
@@ -11782,32 +11782,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21362</t>
+          <t>23512</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12761</t>
+          <t>15556</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30382</t>
+          <t>36497</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11817,32 +11817,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15466</t>
+          <t>16741</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9801</t>
+          <t>10844</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22912</t>
+          <t>24162</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11852,32 +11852,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>36829</t>
+          <t>40253</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27229</t>
+          <t>29707</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49317</t>
+          <t>52731</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,61%</t>
         </is>
       </c>
     </row>
@@ -11895,32 +11895,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4358</t>
+          <t>6866</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1176</t>
+          <t>2237</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>17832</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11930,22 +11930,22 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>2159</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>675</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5835</t>
+          <t>6997</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11965,32 +11965,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>6427</t>
+          <t>9025</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2911</t>
+          <t>3944</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13478</t>
+          <t>19292</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -12008,32 +12008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3373</t>
+          <t>3378</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>940</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9144</t>
+          <t>10266</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12043,32 +12043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3616</t>
+          <t>3764</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1460</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8597</t>
+          <t>8197</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12078,32 +12078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>6989</t>
+          <t>7142</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3134</t>
+          <t>3144</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13772</t>
+          <t>13723</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -12121,17 +12121,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>179857</t>
+          <t>199967</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>179857</t>
+          <t>199967</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>179857</t>
+          <t>199967</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12156,17 +12156,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>150617</t>
+          <t>161008</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>150617</t>
+          <t>161008</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>150617</t>
+          <t>161008</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12191,17 +12191,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>330474</t>
+          <t>360976</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>330474</t>
+          <t>360976</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>330474</t>
+          <t>360976</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12238,32 +12238,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>135913</t>
+          <t>141090</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>123917</t>
+          <t>128908</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>144685</t>
+          <t>150494</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12273,17 +12273,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>104160</t>
+          <t>112023</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>97485</t>
+          <t>104309</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>109629</t>
+          <t>117947</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -12293,12 +12293,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -12308,32 +12308,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>240073</t>
+          <t>253113</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>227592</t>
+          <t>238333</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>250788</t>
+          <t>265215</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,98%</t>
         </is>
       </c>
     </row>
@@ -12351,32 +12351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>18902</t>
+          <t>20535</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10938</t>
+          <t>12025</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30218</t>
+          <t>31902</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12386,32 +12386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7411</t>
+          <t>7445</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3435</t>
+          <t>3384</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12937</t>
+          <t>14077</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12421,32 +12421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>26313</t>
+          <t>27980</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16959</t>
+          <t>17911</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37838</t>
+          <t>41717</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>14,31%</t>
         </is>
       </c>
     </row>
@@ -12464,32 +12464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3813</t>
+          <t>3726</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>805</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9505</t>
+          <t>8578</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12534,32 +12534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>3813</t>
+          <t>3726</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>965</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10039</t>
+          <t>9441</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -12577,7 +12577,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1432</t>
+          <t>1533</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -12587,12 +12587,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7864</t>
+          <t>9228</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -12602,7 +12602,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12612,32 +12612,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4288</t>
+          <t>5142</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>1685</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10296</t>
+          <t>12650</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12647,32 +12647,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>5721</t>
+          <t>6675</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1794</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13917</t>
+          <t>15582</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -12690,17 +12690,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>160060</t>
+          <t>166884</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>160060</t>
+          <t>166884</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>160060</t>
+          <t>166884</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12725,17 +12725,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>115860</t>
+          <t>124610</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>115860</t>
+          <t>124610</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>115860</t>
+          <t>124610</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12760,17 +12760,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>275920</t>
+          <t>291494</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>275920</t>
+          <t>291494</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>275920</t>
+          <t>291494</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12807,32 +12807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>292117</t>
+          <t>52933</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>128757</t>
+          <t>40747</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>351989</t>
+          <t>65668</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12842,32 +12842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>27294</t>
+          <t>30806</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21080</t>
+          <t>24440</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>32989</t>
+          <t>37368</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12877,32 +12877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>319410</t>
+          <t>83739</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>172716</t>
+          <t>69103</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>389581</t>
+          <t>98068</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>51,37%</t>
         </is>
       </c>
     </row>
@@ -12920,32 +12920,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>42894</t>
+          <t>46978</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9309</t>
+          <t>35535</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>138245</t>
+          <t>61340</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -12955,32 +12955,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6105</t>
+          <t>6656</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3049</t>
+          <t>3305</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11447</t>
+          <t>12384</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -12990,32 +12990,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>48998</t>
+          <t>53633</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>13245</t>
+          <t>41392</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>128027</t>
+          <t>66471</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>34,82%</t>
         </is>
       </c>
     </row>
@@ -13033,32 +13033,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>28379</t>
+          <t>32429</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5794</t>
+          <t>22103</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>92189</t>
+          <t>45008</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13068,32 +13068,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6752</t>
+          <t>7342</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3340</t>
+          <t>3580</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11864</t>
+          <t>12615</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13103,32 +13103,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>35131</t>
+          <t>39771</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>27630</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>91293</t>
+          <t>53624</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>28,09%</t>
         </is>
       </c>
     </row>
@@ -13146,32 +13146,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8168</t>
+          <t>8883</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29706</t>
+          <t>22443</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13181,32 +13181,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4694</t>
+          <t>4893</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9168</t>
+          <t>9763</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13216,32 +13216,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>12862</t>
+          <t>13776</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>7088</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>38497</t>
+          <t>27045</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>14,17%</t>
         </is>
       </c>
     </row>
@@ -13259,17 +13259,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>371557</t>
+          <t>141223</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>371557</t>
+          <t>141223</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>371557</t>
+          <t>141223</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13294,17 +13294,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>44845</t>
+          <t>49696</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>44845</t>
+          <t>49696</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>44845</t>
+          <t>49696</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13329,17 +13329,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>416402</t>
+          <t>190919</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>416402</t>
+          <t>190919</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>416402</t>
+          <t>190919</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13376,32 +13376,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>128320</t>
+          <t>146634</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>112838</t>
+          <t>126633</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>146835</t>
+          <t>165325</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13411,32 +13411,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>134337</t>
+          <t>150052</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>122156</t>
+          <t>134730</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>145288</t>
+          <t>161700</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13446,32 +13446,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>262657</t>
+          <t>296686</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>240431</t>
+          <t>271205</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>282834</t>
+          <t>318791</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>62,59%</t>
         </is>
       </c>
     </row>
@@ -13489,32 +13489,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>92868</t>
+          <t>100813</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>75902</t>
+          <t>82884</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>108766</t>
+          <t>118657</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13524,32 +13524,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>43754</t>
+          <t>48792</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34590</t>
+          <t>39691</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>54861</t>
+          <t>62628</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13559,32 +13559,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>136621</t>
+          <t>149606</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>117212</t>
+          <t>129913</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>157930</t>
+          <t>171993</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>33,77%</t>
         </is>
       </c>
     </row>
@@ -13602,32 +13602,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>27697</t>
+          <t>30793</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17316</t>
+          <t>19803</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>40603</t>
+          <t>46356</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -13637,32 +13637,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8741</t>
+          <t>9204</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>4886</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14759</t>
+          <t>14850</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13672,32 +13672,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>36438</t>
+          <t>39997</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>26253</t>
+          <t>28583</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>51623</t>
+          <t>56690</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -13715,32 +13715,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>8816</t>
+          <t>10893</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4390</t>
+          <t>5533</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18343</t>
+          <t>21165</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13750,32 +13750,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>9799</t>
+          <t>12153</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4926</t>
+          <t>6738</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17062</t>
+          <t>21046</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13785,32 +13785,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>18615</t>
+          <t>23046</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11901</t>
+          <t>14747</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29904</t>
+          <t>35222</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -13828,17 +13828,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>257700</t>
+          <t>289133</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>257700</t>
+          <t>289133</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>257700</t>
+          <t>289133</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13863,17 +13863,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>196631</t>
+          <t>220202</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>196631</t>
+          <t>220202</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>196631</t>
+          <t>220202</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13898,17 +13898,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>454331</t>
+          <t>509335</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>454331</t>
+          <t>509335</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>454331</t>
+          <t>509335</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13945,32 +13945,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>51739</t>
+          <t>62863</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>39704</t>
+          <t>47749</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>65376</t>
+          <t>80201</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13980,32 +13980,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>94987</t>
+          <t>76633</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>73854</t>
+          <t>65877</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>128301</t>
+          <t>88817</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14015,32 +14015,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>146727</t>
+          <t>139496</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>120874</t>
+          <t>120244</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>193421</t>
+          <t>158135</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>48,9%</t>
         </is>
       </c>
     </row>
@@ -14058,32 +14058,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>60768</t>
+          <t>75748</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>47854</t>
+          <t>60660</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>74807</t>
+          <t>90912</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14093,32 +14093,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>56456</t>
+          <t>64224</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>28102</t>
+          <t>52828</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>74537</t>
+          <t>75079</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14128,32 +14128,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>117224</t>
+          <t>139971</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>83537</t>
+          <t>121482</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>141302</t>
+          <t>158227</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>48,93%</t>
         </is>
       </c>
     </row>
@@ -14171,32 +14171,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>13172</t>
+          <t>23216</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6542</t>
+          <t>14101</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21284</t>
+          <t>39969</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14206,32 +14206,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>7829</t>
+          <t>9586</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>5118</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13810</t>
+          <t>16068</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14241,32 +14241,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>21001</t>
+          <t>32802</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12681</t>
+          <t>21943</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>32809</t>
+          <t>49241</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>15,23%</t>
         </is>
       </c>
     </row>
@@ -14284,32 +14284,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>6595</t>
+          <t>6923</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2595</t>
+          <t>2716</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>14594</t>
+          <t>14911</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -14319,32 +14319,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3577</t>
+          <t>4177</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1419</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>10101</t>
+          <t>9986</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -14354,32 +14354,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>10172</t>
+          <t>11100</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>5013</t>
+          <t>5578</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>19015</t>
+          <t>19653</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -14397,17 +14397,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>132274</t>
+          <t>168750</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>132274</t>
+          <t>168750</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>132274</t>
+          <t>168750</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14432,17 +14432,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>162849</t>
+          <t>154620</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>162849</t>
+          <t>154620</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>162849</t>
+          <t>154620</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14467,17 +14467,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>295123</t>
+          <t>323369</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>295123</t>
+          <t>323369</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>295123</t>
+          <t>323369</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14514,32 +14514,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>758852</t>
+          <t>569731</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>645122</t>
+          <t>531345</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>920847</t>
+          <t>604079</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>62,54%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14549,32 +14549,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>490246</t>
+          <t>507857</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>466624</t>
+          <t>489618</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>522164</t>
+          <t>531474</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14584,32 +14584,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1249098</t>
+          <t>1077589</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1149191</t>
+          <t>1034814</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1453626</t>
+          <t>1120075</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>66,83%</t>
         </is>
       </c>
     </row>
@@ -14627,32 +14627,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>236794</t>
+          <t>267585</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>128458</t>
+          <t>235070</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>316338</t>
+          <t>299612</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14662,32 +14662,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>129192</t>
+          <t>143858</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>103781</t>
+          <t>125026</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>149022</t>
+          <t>163941</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14697,32 +14697,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>365985</t>
+          <t>411443</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>225007</t>
+          <t>378095</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>440585</t>
+          <t>449147</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>26,8%</t>
         </is>
       </c>
     </row>
@@ -14740,32 +14740,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>77418</t>
+          <t>97031</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>37239</t>
+          <t>77711</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>109502</t>
+          <t>122546</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14775,32 +14775,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>25391</t>
+          <t>28291</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>18071</t>
+          <t>19829</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>34645</t>
+          <t>37814</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14810,32 +14810,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>102809</t>
+          <t>125322</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>65308</t>
+          <t>100279</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>130408</t>
+          <t>152811</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>9,12%</t>
         </is>
       </c>
     </row>
@@ -14853,32 +14853,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>28385</t>
+          <t>31610</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>12852</t>
+          <t>20650</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>45996</t>
+          <t>48704</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14888,32 +14888,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>25974</t>
+          <t>30129</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>17915</t>
+          <t>21398</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>37677</t>
+          <t>42140</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14923,32 +14923,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>54358</t>
+          <t>61739</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>32445</t>
+          <t>45449</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>73021</t>
+          <t>79460</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -14966,17 +14966,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1101448</t>
+          <t>965957</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1101448</t>
+          <t>965957</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1101448</t>
+          <t>965957</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -15001,17 +15001,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>670803</t>
+          <t>710136</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>670803</t>
+          <t>710136</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>670803</t>
+          <t>710136</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15036,17 +15036,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1772251</t>
+          <t>1676093</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1772251</t>
+          <t>1676093</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1772251</t>
+          <t>1676093</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
